--- a/apps/PythonAnywhere/website/static/healthie/documents/modtypes_features_test_v1.0.xlsx
+++ b/apps/PythonAnywhere/website/static/healthie/documents/modtypes_features_test_v1.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" state="visible" r:id="rId2"/>
@@ -37213,7 +37213,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="45.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="98.65"/>
